--- a/rtss-pre1917/territory-chart.xlsx
+++ b/rtss-pre1917/territory-chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3923A340-5055-4C36-B22E-179A242EAAA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA7B0FF-7FA9-4E0F-AB40-FF54D53F7897}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="705" yWindow="2340" windowWidth="32910" windowHeight="19110" xr2:uid="{DA233FF1-1F5C-4C19-B65A-485A17C190AF}"/>
+    <workbookView xWindow="1710" yWindow="1275" windowWidth="23610" windowHeight="20055" xr2:uid="{DA233FF1-1F5C-4C19-B65A-485A17C190AF}"/>
   </bookViews>
   <sheets>
     <sheet name="charts" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="10">
   <si>
     <t> </t>
   </si>
@@ -843,61 +843,61 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
+                  <c:v>9.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>31.1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>38.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>43.3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>53.1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>40.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>43.2</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>45.1</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>44.4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>43.6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>48.1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>44.9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>42.7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>46.2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>44.6</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>42.8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>38.4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>42.7</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>47.6</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>44.4</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>41.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>41.8</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>41.6</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>31.7</c:v>
+                  <c:v>41.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1020,61 +1020,61 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>28.5</c:v>
+                  <c:v>5.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25.3</c:v>
+                  <c:v>13.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24.5</c:v>
+                  <c:v>15.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>29.1</c:v>
+                  <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>22.9</c:v>
+                  <c:v>21.9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.6</c:v>
+                  <c:v>19.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>26.4</c:v>
+                  <c:v>20.399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>24.9</c:v>
+                  <c:v>19.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>24.3</c:v>
+                  <c:v>15.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>27</c:v>
+                  <c:v>15.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>24.9</c:v>
+                  <c:v>20.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>26.6</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>26.8</c:v>
+                  <c:v>27.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>26.9</c:v>
+                  <c:v>18.8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>32.799999999999997</c:v>
+                  <c:v>18.100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>31.3</c:v>
+                  <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>32</c:v>
+                  <c:v>22.3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>31.7</c:v>
+                  <c:v>20.9</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>16.600000000000001</c:v>
+                  <c:v>18.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4623,37 +4623,37 @@
         <v>0</v>
       </c>
       <c r="C66" s="1">
-        <v>1827194</v>
+        <v>155295</v>
       </c>
       <c r="D66" s="3">
-        <v>46.9</v>
+        <v>13.3</v>
       </c>
       <c r="E66" s="3">
-        <v>29.7</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="F66" s="3">
-        <v>17.2</v>
+        <v>5</v>
       </c>
       <c r="G66" s="1">
-        <v>85704</v>
+        <v>2062</v>
       </c>
       <c r="H66" s="1">
-        <v>54186</v>
+        <v>1288</v>
       </c>
       <c r="I66" s="5">
-        <v>-913</v>
+        <v>55</v>
       </c>
       <c r="J66" s="1">
-        <v>1902010</v>
+        <v>222321</v>
       </c>
       <c r="K66" s="3">
-        <v>45.1</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="L66" s="3">
-        <v>28.5</v>
+        <v>5.8</v>
       </c>
       <c r="M66" s="4">
-        <v>16.600000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>0</v>
@@ -4688,37 +4688,37 @@
         <v>0</v>
       </c>
       <c r="C67" s="1">
-        <v>1936403</v>
+        <v>177351</v>
       </c>
       <c r="D67" s="3">
-        <v>44.3</v>
+        <v>30.9</v>
       </c>
       <c r="E67" s="3">
-        <v>25.2</v>
+        <v>17.3</v>
       </c>
       <c r="F67" s="3">
-        <v>19</v>
+        <v>13.6</v>
       </c>
       <c r="G67" s="1">
-        <v>85731</v>
+        <v>5476</v>
       </c>
       <c r="H67" s="1">
-        <v>48849</v>
+        <v>3068</v>
       </c>
       <c r="I67" s="5">
-        <v>924</v>
+        <v>103</v>
       </c>
       <c r="J67" s="1">
-        <v>1932615</v>
+        <v>223150</v>
       </c>
       <c r="K67" s="3">
-        <v>44.4</v>
+        <v>24.5</v>
       </c>
       <c r="L67" s="3">
-        <v>25.3</v>
+        <v>13.7</v>
       </c>
       <c r="M67" s="4">
-        <v>19.100000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>0</v>
@@ -4753,37 +4753,37 @@
         <v>0</v>
       </c>
       <c r="C68" s="1">
-        <v>1966905</v>
+        <v>198836</v>
       </c>
       <c r="D68" s="3">
-        <v>43.6</v>
+        <v>29.6</v>
       </c>
       <c r="E68" s="3">
-        <v>24.6</v>
+        <v>17.8</v>
       </c>
       <c r="F68" s="3">
-        <v>19</v>
+        <v>11.9</v>
       </c>
       <c r="G68" s="1">
-        <v>85818</v>
+        <v>5893</v>
       </c>
       <c r="H68" s="1">
-        <v>48360</v>
+        <v>3530</v>
       </c>
       <c r="I68" s="5">
-        <v>1308</v>
+        <v>480</v>
       </c>
       <c r="J68" s="1">
-        <v>1970421</v>
+        <v>225661</v>
       </c>
       <c r="K68" s="3">
-        <v>43.6</v>
+        <v>26.1</v>
       </c>
       <c r="L68" s="3">
-        <v>24.5</v>
+        <v>15.6</v>
       </c>
       <c r="M68" s="4">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>0</v>
@@ -4818,37 +4818,37 @@
         <v>0</v>
       </c>
       <c r="C69" s="1">
-        <v>1971225</v>
+        <v>227950</v>
       </c>
       <c r="D69" s="3">
-        <v>49</v>
+        <v>31.9</v>
       </c>
       <c r="E69" s="3">
-        <v>29.7</v>
+        <v>21.5</v>
       </c>
       <c r="F69" s="3">
-        <v>19.3</v>
+        <v>10.4</v>
       </c>
       <c r="G69" s="1">
-        <v>96569</v>
+        <v>7276</v>
       </c>
       <c r="H69" s="1">
-        <v>58534</v>
+        <v>4906</v>
       </c>
       <c r="I69" s="5">
-        <v>-397</v>
+        <v>1019</v>
       </c>
       <c r="J69" s="1">
-        <v>2009187</v>
+        <v>228504</v>
       </c>
       <c r="K69" s="3">
-        <v>48.1</v>
+        <v>31.8</v>
       </c>
       <c r="L69" s="3">
-        <v>29.1</v>
+        <v>21.5</v>
       </c>
       <c r="M69" s="4">
-        <v>18.899999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>0</v>
@@ -4883,37 +4883,37 @@
         <v>0</v>
       </c>
       <c r="C70" s="1">
-        <v>2043871</v>
+        <v>243666</v>
       </c>
       <c r="D70" s="3">
-        <v>45</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="E70" s="3">
-        <v>23</v>
+        <v>20.9</v>
       </c>
       <c r="F70" s="3">
-        <v>22.1</v>
+        <v>12.4</v>
       </c>
       <c r="G70" s="1">
-        <v>91998</v>
+        <v>8115</v>
       </c>
       <c r="H70" s="1">
-        <v>46912</v>
+        <v>5085</v>
       </c>
       <c r="I70" s="5">
-        <v>-455</v>
+        <v>5902</v>
       </c>
       <c r="J70" s="1">
-        <v>2046825</v>
+        <v>231893</v>
       </c>
       <c r="K70" s="3">
-        <v>44.9</v>
+        <v>35</v>
       </c>
       <c r="L70" s="3">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="M70" s="4">
-        <v>22</v>
+        <v>13.1</v>
       </c>
       <c r="N70" s="1" t="s">
         <v>0</v>
@@ -4948,37 +4948,37 @@
         <v>0</v>
       </c>
       <c r="C71" s="1">
-        <v>2087238</v>
+        <v>268592</v>
       </c>
       <c r="D71" s="3">
-        <v>42.8</v>
+        <v>30</v>
       </c>
       <c r="E71" s="3">
-        <v>22.6</v>
+        <v>17.7</v>
       </c>
       <c r="F71" s="3">
-        <v>20.2</v>
+        <v>12.3</v>
       </c>
       <c r="G71" s="1">
-        <v>89324</v>
+        <v>8060</v>
       </c>
       <c r="H71" s="1">
-        <v>47254</v>
+        <v>4744</v>
       </c>
       <c r="I71" s="5">
-        <v>-27</v>
+        <v>2906</v>
       </c>
       <c r="J71" s="1">
-        <v>2091456</v>
+        <v>240825</v>
       </c>
       <c r="K71" s="3">
-        <v>42.7</v>
+        <v>33.5</v>
       </c>
       <c r="L71" s="3">
-        <v>22.6</v>
+        <v>19.7</v>
       </c>
       <c r="M71" s="4">
-        <v>20.100000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>0</v>
@@ -5013,37 +5013,37 @@
         <v>0</v>
       </c>
       <c r="C72" s="1">
-        <v>2142537</v>
+        <v>281000</v>
       </c>
       <c r="D72" s="3">
-        <v>46</v>
+        <v>31.4</v>
       </c>
       <c r="E72" s="3">
-        <v>26.3</v>
+        <v>18</v>
       </c>
       <c r="F72" s="3">
-        <v>19.7</v>
+        <v>13.4</v>
       </c>
       <c r="G72" s="1">
-        <v>98577</v>
+        <v>8815</v>
       </c>
       <c r="H72" s="1">
-        <v>56392</v>
+        <v>5044</v>
       </c>
       <c r="I72" s="5">
-        <v>-272</v>
+        <v>6402</v>
       </c>
       <c r="J72" s="1">
-        <v>2133499</v>
+        <v>247047</v>
       </c>
       <c r="K72" s="3">
-        <v>46.2</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="L72" s="3">
-        <v>26.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M72" s="4">
-        <v>19.8</v>
+        <v>15.3</v>
       </c>
       <c r="N72" s="1" t="s">
         <v>0</v>
@@ -5078,37 +5078,37 @@
         <v>0</v>
       </c>
       <c r="C73" s="1">
-        <v>2124487</v>
+        <v>300370</v>
       </c>
       <c r="D73" s="3">
-        <v>45.7</v>
+        <v>33.4</v>
       </c>
       <c r="E73" s="3">
-        <v>25.5</v>
+        <v>16.8</v>
       </c>
       <c r="F73" s="3">
-        <v>20.2</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="G73" s="1">
-        <v>97034</v>
+        <v>10029</v>
       </c>
       <c r="H73" s="1">
-        <v>54167</v>
+        <v>5037</v>
       </c>
       <c r="I73" s="5">
-        <v>-2119</v>
+        <v>7301</v>
       </c>
       <c r="J73" s="1">
-        <v>2175824</v>
+        <v>257220</v>
       </c>
       <c r="K73" s="3">
-        <v>44.6</v>
+        <v>39</v>
       </c>
       <c r="L73" s="3">
-        <v>24.9</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="M73" s="4">
-        <v>19.7</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="N73" s="1" t="s">
         <v>0</v>
@@ -5140,40 +5140,40 @@
         <v>1904</v>
       </c>
       <c r="B74" s="1">
-        <v>2195200</v>
+        <v>242900</v>
       </c>
       <c r="C74" s="1">
-        <v>2183638</v>
+        <v>330204</v>
       </c>
       <c r="D74" s="3">
-        <v>43.5</v>
+        <v>26.8</v>
       </c>
       <c r="E74" s="3">
-        <v>24.7</v>
+        <v>12.9</v>
       </c>
       <c r="F74" s="3">
-        <v>18.8</v>
+        <v>13.9</v>
       </c>
       <c r="G74" s="1">
-        <v>94969</v>
+        <v>8834</v>
       </c>
       <c r="H74" s="1">
-        <v>53942</v>
+        <v>4260</v>
       </c>
       <c r="I74" s="5">
-        <v>-2674</v>
+        <v>-143</v>
       </c>
       <c r="J74" s="1">
-        <v>2216799</v>
+        <v>269513</v>
       </c>
       <c r="K74" s="3">
-        <v>42.8</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="L74" s="3">
-        <v>24.3</v>
+        <v>15.8</v>
       </c>
       <c r="M74" s="4">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="N74" s="1" t="s">
         <v>0</v>
@@ -5205,40 +5205,40 @@
         <v>1905</v>
       </c>
       <c r="B75" s="1">
-        <v>2236900</v>
+        <v>246800</v>
       </c>
       <c r="C75" s="1">
-        <v>2182421</v>
+        <v>252210</v>
       </c>
       <c r="D75" s="3">
-        <v>39.700000000000003</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="E75" s="3">
-        <v>27.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F75" s="3">
-        <v>11.8</v>
+        <v>16.8</v>
       </c>
       <c r="G75" s="1">
-        <v>86579</v>
+        <v>8506</v>
       </c>
       <c r="H75" s="1">
-        <v>60921</v>
+        <v>4273</v>
       </c>
       <c r="I75" s="5">
-        <v>-8334</v>
+        <v>-36</v>
       </c>
       <c r="J75" s="1">
-        <v>2255152</v>
+        <v>273944</v>
       </c>
       <c r="K75" s="3">
-        <v>38.4</v>
+        <v>31.1</v>
       </c>
       <c r="L75" s="3">
-        <v>27</v>
+        <v>15.6</v>
       </c>
       <c r="M75" s="4">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="N75" s="1" t="s">
         <v>0</v>
@@ -5270,37 +5270,37 @@
         <v>1906</v>
       </c>
       <c r="B76" s="1">
-        <v>2262400</v>
+        <v>252100</v>
       </c>
       <c r="C76" s="1">
-        <v>2209627</v>
+        <v>239970</v>
       </c>
       <c r="D76" s="3">
-        <v>43.9</v>
+        <v>44.9</v>
       </c>
       <c r="E76" s="3">
-        <v>25.6</v>
+        <v>24.2</v>
       </c>
       <c r="F76" s="3">
-        <v>18.3</v>
+        <v>20.6</v>
       </c>
       <c r="G76" s="1">
-        <v>97111</v>
+        <v>10768</v>
       </c>
       <c r="H76" s="1">
-        <v>56609</v>
+        <v>5818</v>
       </c>
       <c r="I76" s="5">
-        <v>-20526</v>
+        <v>13290</v>
       </c>
       <c r="J76" s="1">
-        <v>2272805</v>
+        <v>278141</v>
       </c>
       <c r="K76" s="3">
-        <v>42.7</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="L76" s="3">
-        <v>24.9</v>
+        <v>20.9</v>
       </c>
       <c r="M76" s="4">
         <v>17.8</v>
@@ -5335,40 +5335,40 @@
         <v>1907</v>
       </c>
       <c r="B77" s="1">
-        <v>2302100</v>
+        <v>267300</v>
       </c>
       <c r="C77" s="1">
-        <v>2278351</v>
+        <v>359138</v>
       </c>
       <c r="D77" s="3">
-        <v>47.9</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="E77" s="3">
-        <v>26.8</v>
+        <v>21.8</v>
       </c>
       <c r="F77" s="3">
-        <v>21.1</v>
+        <v>13.9</v>
       </c>
       <c r="G77" s="1">
-        <v>109176</v>
+        <v>12819</v>
       </c>
       <c r="H77" s="1">
-        <v>61012</v>
+        <v>7842</v>
       </c>
       <c r="I77" s="5">
-        <v>-9411</v>
+        <v>74512</v>
       </c>
       <c r="J77" s="1">
-        <v>2292781</v>
+        <v>296382</v>
       </c>
       <c r="K77" s="3">
-        <v>47.6</v>
+        <v>43.3</v>
       </c>
       <c r="L77" s="3">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="M77" s="4">
-        <v>21</v>
+        <v>16.8</v>
       </c>
       <c r="N77" s="1" t="s">
         <v>0</v>
@@ -5400,40 +5400,40 @@
         <v>1908</v>
       </c>
       <c r="B78" s="1">
-        <v>2344800</v>
+        <v>289600</v>
       </c>
       <c r="C78" s="1">
-        <v>2317803</v>
+        <v>516767</v>
       </c>
       <c r="D78" s="3">
-        <v>44.6</v>
+        <v>38.6</v>
       </c>
       <c r="E78" s="3">
-        <v>26.9</v>
+        <v>20</v>
       </c>
       <c r="F78" s="3">
-        <v>17.7</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="G78" s="1">
-        <v>103466</v>
+        <v>19955</v>
       </c>
       <c r="H78" s="1">
-        <v>62461</v>
+        <v>10335</v>
       </c>
       <c r="I78" s="5">
-        <v>-6957</v>
+        <v>20590</v>
       </c>
       <c r="J78" s="1">
-        <v>2331906</v>
+        <v>376141</v>
       </c>
       <c r="K78" s="3">
-        <v>44.4</v>
+        <v>53.1</v>
       </c>
       <c r="L78" s="3">
-        <v>26.8</v>
+        <v>27.5</v>
       </c>
       <c r="M78" s="4">
-        <v>17.600000000000001</v>
+        <v>25.6</v>
       </c>
       <c r="N78" s="1" t="s">
         <v>0</v>
@@ -5465,40 +5465,40 @@
         <v>1909</v>
       </c>
       <c r="B79" s="1">
-        <v>2393100</v>
+        <v>303700</v>
       </c>
       <c r="C79" s="1">
-        <v>2365034</v>
+        <v>530805</v>
       </c>
       <c r="D79" s="3">
-        <v>46</v>
+        <v>30.8</v>
       </c>
       <c r="E79" s="3">
-        <v>26.9</v>
+        <v>14.4</v>
       </c>
       <c r="F79" s="3">
-        <v>19.100000000000001</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="G79" s="1">
-        <v>108840</v>
+        <v>16336</v>
       </c>
       <c r="H79" s="1">
-        <v>63591</v>
+        <v>7639</v>
       </c>
       <c r="I79" s="5">
-        <v>-8395</v>
+        <v>18588</v>
       </c>
       <c r="J79" s="1">
-        <v>2365954</v>
+        <v>406352</v>
       </c>
       <c r="K79" s="3">
-        <v>46</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="L79" s="3">
-        <v>26.9</v>
+        <v>18.8</v>
       </c>
       <c r="M79" s="4">
-        <v>19.100000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="N79" s="1" t="s">
         <v>0</v>
@@ -5530,40 +5530,40 @@
         <v>1910</v>
       </c>
       <c r="B80" s="1">
-        <v>2441200</v>
+        <v>316900</v>
       </c>
       <c r="C80" s="1">
-        <v>2405171</v>
+        <v>546700</v>
       </c>
       <c r="D80" s="3">
-        <v>43</v>
+        <v>31.6</v>
       </c>
       <c r="E80" s="3">
-        <v>32.700000000000003</v>
+        <v>14.4</v>
       </c>
       <c r="F80" s="3">
-        <v>10.3</v>
+        <v>17.2</v>
       </c>
       <c r="G80" s="1">
-        <v>103378</v>
+        <v>17262</v>
       </c>
       <c r="H80" s="1">
-        <v>78708</v>
+        <v>7855</v>
       </c>
       <c r="I80" s="5">
-        <v>-10294</v>
+        <v>9272</v>
       </c>
       <c r="J80" s="1">
-        <v>2402809</v>
+        <v>433637</v>
       </c>
       <c r="K80" s="3">
-        <v>43</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="L80" s="3">
-        <v>32.799999999999997</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="M80" s="4">
-        <v>10.3</v>
+        <v>21.7</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>0</v>
@@ -5595,40 +5595,40 @@
         <v>1911</v>
       </c>
       <c r="B81" s="1">
-        <v>2490200</v>
+        <v>570400</v>
       </c>
       <c r="C81" s="1">
-        <v>2448354</v>
+        <v>541792</v>
       </c>
       <c r="D81" s="3">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E81" s="3">
-        <v>30.9</v>
+        <v>18</v>
       </c>
       <c r="F81" s="3">
-        <v>10.1</v>
+        <v>15</v>
       </c>
       <c r="G81" s="1">
-        <v>100357</v>
+        <v>17890</v>
       </c>
       <c r="H81" s="1">
-        <v>75591</v>
+        <v>9739</v>
       </c>
       <c r="I81" s="5">
-        <v>2067</v>
+        <v>7494</v>
       </c>
       <c r="J81" s="1">
-        <v>2417344</v>
+        <v>452597</v>
       </c>
       <c r="K81" s="3">
-        <v>41.5</v>
+        <v>39.5</v>
       </c>
       <c r="L81" s="3">
-        <v>31.3</v>
+        <v>21.5</v>
       </c>
       <c r="M81" s="4">
-        <v>10.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="N81" s="1" t="s">
         <v>0</v>
@@ -5660,40 +5660,40 @@
         <v>1912</v>
       </c>
       <c r="B82" s="1">
-        <v>2538900</v>
+        <v>610500</v>
       </c>
       <c r="C82" s="1">
-        <v>2472542</v>
+        <v>580073</v>
       </c>
       <c r="D82" s="3">
-        <v>41.3</v>
+        <v>34.9</v>
       </c>
       <c r="E82" s="3">
-        <v>31.6</v>
+        <v>18</v>
       </c>
       <c r="F82" s="3">
-        <v>9.6999999999999993</v>
+        <v>17</v>
       </c>
       <c r="G82" s="1">
-        <v>102159</v>
+        <v>20270</v>
       </c>
       <c r="H82" s="1">
-        <v>78205</v>
+        <v>10435</v>
       </c>
       <c r="I82" s="5">
-        <v>-3448</v>
+        <v>9981</v>
       </c>
       <c r="J82" s="1">
-        <v>2444177</v>
+        <v>468682</v>
       </c>
       <c r="K82" s="3">
-        <v>41.8</v>
+        <v>43.2</v>
       </c>
       <c r="L82" s="3">
-        <v>32</v>
+        <v>22.3</v>
       </c>
       <c r="M82" s="4">
-        <v>9.8000000000000007</v>
+        <v>21</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>0</v>
@@ -5725,40 +5725,40 @@
         <v>1913</v>
       </c>
       <c r="B83" s="1">
-        <v>2588400</v>
+        <v>643400</v>
       </c>
       <c r="C83" s="1">
-        <v>2448642</v>
+        <v>623072</v>
       </c>
       <c r="D83" s="3">
-        <v>41.9</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="E83" s="3">
-        <v>31.9</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="F83" s="3">
-        <v>10</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="G83" s="1">
-        <v>102503</v>
+        <v>22020</v>
       </c>
       <c r="H83" s="1">
-        <v>78027</v>
+        <v>10223</v>
       </c>
       <c r="I83" s="5">
-        <v>-6621</v>
+        <v>8464</v>
       </c>
       <c r="J83" s="1">
-        <v>2464684</v>
+        <v>488730</v>
       </c>
       <c r="K83" s="3">
-        <v>41.6</v>
+        <v>45.1</v>
       </c>
       <c r="L83" s="3">
-        <v>31.7</v>
+        <v>20.9</v>
       </c>
       <c r="M83" s="4">
-        <v>9.9</v>
+        <v>24.1</v>
       </c>
       <c r="N83" s="1" t="s">
         <v>0</v>
@@ -5790,65 +5790,44 @@
         <v>1914</v>
       </c>
       <c r="B84" s="1">
-        <v>2657300</v>
+        <v>647100</v>
       </c>
       <c r="C84" s="1">
-        <v>2472605</v>
+        <v>658585</v>
       </c>
       <c r="D84" s="3">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="E84" s="3">
-        <v>16.7</v>
+        <v>14.1</v>
       </c>
       <c r="F84" s="3">
-        <v>15.1</v>
+        <v>17.8</v>
       </c>
       <c r="G84" s="1">
-        <v>78693</v>
+        <v>21056</v>
       </c>
       <c r="H84" s="1">
-        <v>41275</v>
+        <v>9312</v>
       </c>
       <c r="I84" s="5">
-        <v>-6350</v>
+        <v>11102</v>
       </c>
       <c r="J84" s="1">
-        <v>2482560</v>
+        <v>509075</v>
       </c>
       <c r="K84" s="3">
-        <v>31.7</v>
+        <v>41.4</v>
       </c>
       <c r="L84" s="3">
-        <v>16.600000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="M84" s="4">
-        <v>15.1</v>
-      </c>
-      <c r="N84" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="O84" t="s">
-        <v>0</v>
-      </c>
-      <c r="P84" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>0</v>
-      </c>
-      <c r="R84" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="S84" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="T84" t="s">
-        <v>0</v>
-      </c>
-      <c r="U84" t="s">
-        <v>0</v>
-      </c>
+        <v>23.1</v>
+      </c>
+      <c r="N84" s="1"/>
+      <c r="R84" s="1"/>
+      <c r="S84" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
